--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N88_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N88_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.317225419947261</v>
+        <v>1.02654913074143</v>
       </c>
       <c r="D2" t="n">
-        <v>5.718976373411345</v>
+        <v>0.9293336606793436</v>
       </c>
       <c r="E2" t="n">
-        <v>17.62390525309745</v>
+        <v>2.863884603628335</v>
       </c>
       <c r="F2" t="n">
-        <v>17.40626929163242</v>
+        <v>2.828518759890267</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.7658710850876</v>
+        <v>7.924454051326736</v>
       </c>
       <c r="D3" t="n">
-        <v>48.15475473276988</v>
+        <v>7.825147644075106</v>
       </c>
       <c r="E3" t="n">
-        <v>17.62390525309745</v>
+        <v>2.863884603628335</v>
       </c>
       <c r="F3" t="n">
-        <v>17.40626929163242</v>
+        <v>2.828518759890267</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.208454014527009</v>
+        <v>0.196373777360639</v>
       </c>
       <c r="D4" t="n">
-        <v>1.498567146433628</v>
+        <v>0.2435171612954646</v>
       </c>
       <c r="E4" t="n">
-        <v>17.62390525309745</v>
+        <v>2.863884603628335</v>
       </c>
       <c r="F4" t="n">
-        <v>17.40626929163242</v>
+        <v>2.828518759890267</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.65154388151294</v>
+        <v>5.630875880745854</v>
       </c>
       <c r="D5" t="n">
-        <v>34.07975631605851</v>
+        <v>5.537960401359507</v>
       </c>
       <c r="E5" t="n">
-        <v>17.62390525309745</v>
+        <v>2.863884603628335</v>
       </c>
       <c r="F5" t="n">
-        <v>17.40626929163242</v>
+        <v>2.828518759890267</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.97385784867161</v>
+        <v>3.570751900409136</v>
       </c>
       <c r="D6" t="n">
-        <v>22.12326972619414</v>
+        <v>3.595031330506548</v>
       </c>
       <c r="E6" t="n">
-        <v>17.62390525309745</v>
+        <v>2.863884603628335</v>
       </c>
       <c r="F6" t="n">
-        <v>17.40626929163242</v>
+        <v>2.828518759890267</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
